--- a/TabeleExcel/Tabele_Id/Employees.xlsx
+++ b/TabeleExcel/Tabele_Id/Employees.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="128">
   <si>
     <t xml:space="preserve">id_employee</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">Romanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">Michael</t>
@@ -489,11 +492,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -842,8 +845,12 @@
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
@@ -853,16 +860,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>40330</v>
@@ -874,10 +881,10 @@
         <v>8000</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>29356</v>
@@ -900,16 +907,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>41167</v>
@@ -924,7 +931,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>28814</v>
@@ -947,16 +954,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>42024</v>
@@ -968,10 +975,10 @@
         <v>10000</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>31088</v>
@@ -994,16 +1001,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>43169</v>
@@ -1018,7 +1025,7 @@
         <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>33059</v>
@@ -1041,16 +1048,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>41968</v>
@@ -1065,7 +1072,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>30224</v>
@@ -1088,16 +1095,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>43221</v>
@@ -1112,7 +1119,7 @@
         <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>33675</v>
@@ -1135,16 +1142,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>43661</v>
@@ -1156,10 +1163,10 @@
         <v>4200</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>34203</v>
@@ -1182,16 +1189,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>43840</v>
@@ -1206,7 +1213,7 @@
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>35038</v>
@@ -1229,16 +1236,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>42845</v>
@@ -1250,10 +1257,10 @@
         <v>5000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>33331</v>
@@ -1276,16 +1283,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>43713</v>
@@ -1300,7 +1307,7 @@
         <v>19</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>33163</v>
@@ -1323,16 +1330,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>44241</v>
@@ -1344,10 +1351,10 @@
         <v>5200</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>32687</v>
@@ -1370,16 +1377,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>43330</v>
@@ -1391,10 +1398,10 @@
         <v>6000</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>32893</v>
@@ -1417,16 +1424,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>43912</v>
@@ -1441,7 +1448,7 @@
         <v>19</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>34463</v>
@@ -1464,16 +1471,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>44530</v>
@@ -1485,10 +1492,10 @@
         <v>6200</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>33919</v>
@@ -1511,16 +1518,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>43470</v>
@@ -1535,7 +1542,7 @@
         <v>19</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>34014</v>
@@ -1558,16 +1565,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>43992</v>
@@ -1579,10 +1586,10 @@
         <v>5300</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>34536</v>
@@ -1605,16 +1612,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>44491</v>
@@ -1629,7 +1636,7 @@
         <v>19</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>35012</v>
@@ -1652,16 +1659,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>43437</v>
@@ -1673,10 +1680,10 @@
         <v>4500</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>32217</v>
@@ -1699,16 +1706,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>43889</v>
@@ -1723,7 +1730,7 @@
         <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>33843</v>
@@ -1746,16 +1753,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>44388</v>
@@ -1767,10 +1774,10 @@
         <v>4300</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>34687</v>
@@ -1793,16 +1800,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>45527</v>
@@ -1817,7 +1824,7 @@
         <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>37706</v>

--- a/TabeleExcel/Tabele_Id/Employees.xlsx
+++ b/TabeleExcel/Tabele_Id/Employees.xlsx
@@ -414,7 +414,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -438,6 +438,14 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -445,12 +453,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -487,16 +501,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -534,7 +560,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -760,1120 +786,1123 @@
   </sheetPr>
   <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.67"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="5" t="n">
         <v>39448</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="5" t="n">
         <v>27395</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="5" t="n">
         <v>40330</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="5" t="n">
         <v>29356</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="1" t="n">
+      <c r="L3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="5" t="n">
         <v>41167</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="4" t="n">
         <v>9000</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="5" t="n">
         <v>28814</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="1" t="n">
+      <c r="L4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="5" t="n">
         <v>42024</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="5" t="n">
         <v>31088</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="1" t="n">
+      <c r="L5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="5" t="n">
         <v>43169</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="4" t="n">
         <v>8500</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="5" t="n">
         <v>33059</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1" t="n">
+      <c r="L6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="5" t="n">
         <v>41968</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="4" t="n">
         <v>8200</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="5" t="n">
         <v>30224</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="1" t="n">
+      <c r="L7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="5" t="n">
         <v>43221</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="4" t="n">
         <v>4000</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="5" t="n">
         <v>33675</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="1" t="n">
+      <c r="L8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="5" t="n">
         <v>43661</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="4" t="n">
         <v>4200</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="5" t="n">
         <v>34203</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="1" t="n">
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="5" t="n">
         <v>43840</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="4" t="n">
         <v>3800</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="5" t="n">
         <v>35038</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="1" t="n">
+      <c r="L10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="5" t="n">
         <v>42845</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="5" t="n">
         <v>33331</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="1" t="n">
+      <c r="L11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="N11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="O11" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="5" t="n">
         <v>43713</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="4" t="n">
         <v>4800</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="5" t="n">
         <v>33163</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="1" t="n">
+      <c r="L12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="5" t="n">
         <v>44241</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="4" t="n">
         <v>5200</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="5" t="n">
         <v>32687</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="1" t="n">
+      <c r="L13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="5" t="n">
         <v>43330</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="5" t="n">
         <v>32893</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="1" t="n">
+      <c r="L14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="O14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="5" t="n">
         <v>43912</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="4" t="n">
         <v>5800</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="5" t="n">
         <v>34463</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="1" t="n">
+      <c r="L15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="N15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="O15" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="5" t="n">
         <v>44530</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="4" t="n">
         <v>6200</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="5" t="n">
         <v>33919</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="1" t="n">
+      <c r="L16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="N16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="5" t="n">
         <v>43470</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="4" t="n">
         <v>5500</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="5" t="n">
         <v>34014</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="1" t="n">
+      <c r="L17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="N17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="O17" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="5" t="n">
         <v>43992</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>5300</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="5" t="n">
         <v>34536</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="1" t="n">
+      <c r="L18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="N18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="O18" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="5" t="n">
         <v>44491</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="4" t="n">
         <v>5800</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="5" t="n">
         <v>35012</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="1" t="n">
+      <c r="L19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="N19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="O19" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="5" t="n">
         <v>43437</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="4" t="n">
         <v>4500</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="5" t="n">
         <v>32217</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="1" t="n">
+      <c r="L20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="N20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="O20" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="5" t="n">
         <v>43889</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="4" t="n">
         <v>4700</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="5" t="n">
         <v>33843</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="1" t="n">
+      <c r="L21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="N21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="O21" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="5" t="n">
         <v>44388</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="4" t="n">
         <v>4300</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="5" t="n">
         <v>34687</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="1" t="n">
+      <c r="L22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O22" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="5" t="n">
         <v>45527</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="G23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="4" t="n">
         <v>4400</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="5" t="n">
         <v>37706</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="1" t="n">
+      <c r="L23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="N23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="O23" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="2"/>
+      <c r="E24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="2"/>
+      <c r="E25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="2"/>
+      <c r="E26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="2"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="2"/>
+      <c r="E28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="2"/>
+      <c r="E29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="2"/>
+      <c r="E30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="2"/>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="2"/>
+      <c r="E32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="2"/>
+      <c r="E33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="2"/>
+      <c r="E34" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E35:E999">
